--- a/users/ken.aizawa/02_basic/excel/kadai.xlex.xlsx
+++ b/users/ken.aizawa/02_basic/excel/kadai.xlex.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ken_aizawa\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\epkotsoftware\training\users\ken.aizawa\02_basic\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8289C9-8CC0-44C1-8953-4DA0F8876957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{351E59A0-F9ED-4709-8119-9204076F08EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="売上管理票" sheetId="1" r:id="rId1"/>
@@ -1475,6 +1475,51 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1516,51 +1561,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="55">
@@ -2147,7 +2147,7 @@
         <v>580401</v>
       </c>
       <c r="E6" s="3">
-        <f t="shared" ref="E6:P6" si="1">SUM(E4,-E5)</f>
+        <f t="shared" ref="E6:O6" si="1">SUM(E4,-E5)</f>
         <v>219853</v>
       </c>
       <c r="F6" s="3">
@@ -2452,7 +2452,7 @@
         <v>1963386</v>
       </c>
       <c r="E12" s="3">
-        <f t="shared" ref="E12:P12" si="5">SUM(E10,-E11)</f>
+        <f t="shared" ref="E12:O12" si="5">SUM(E10,-E11)</f>
         <v>5173582</v>
       </c>
       <c r="F12" s="3">
@@ -3232,7 +3232,19 @@
         <v>不合格</v>
       </c>
       <c r="H4" s="76" t="str">
-        <f>IF(COUNTIF($C4:$E4,"&gt;=" &amp; $B$11)&gt;=2,"よく出来ました！","")</f>
+        <f>IF(
+  AND(C4&gt;=$B$11, D4&gt;=$B$11),
+  "よく出来ました！",
+  IF(
+    AND(C4&gt;=$B$11, E4&gt;=$B$11),
+    "よく出来ました！",
+    IF(
+      AND(D4&gt;=$B$11, E4&gt;=$B$11),
+      "よく出来ました！",
+      ""
+    )
+  )
+)</f>
         <v>よく出来ました！</v>
       </c>
       <c r="I4" s="76" t="str">
@@ -3265,11 +3277,23 @@
         <v/>
       </c>
       <c r="H5" s="76" t="str">
-        <f t="shared" ref="H5:H8" si="2">IF(COUNTIF(C5:E5,"&gt;=" &amp; $B$11)&gt;=2,"よく出来ました！","")</f>
+        <f>IF(
+  AND(C5&gt;=$B$11, D5&gt;=$B$11),
+  "よく出来ました！",
+  IF(
+    AND(C5&gt;=$B$11, E5&gt;=$B$11),
+    "よく出来ました！",
+    IF(
+      AND(D5&gt;=$B$11, E5&gt;=$B$11),
+      "よく出来ました！",
+      ""
+    )
+  )
+)</f>
         <v/>
       </c>
       <c r="I5" s="76" t="str">
-        <f t="shared" ref="I5:I8" si="3">IF(COUNTIF($C5:$E5,"&gt;=" &amp; $B$11)&gt;=2,"よく出来ました！","")</f>
+        <f t="shared" ref="I5:I8" si="2">IF(COUNTIF($C5:$E5,"&gt;=" &amp; $B$11)&gt;=2,"よく出来ました！","")</f>
         <v/>
       </c>
     </row>
@@ -3295,11 +3319,23 @@
         <v>不合格</v>
       </c>
       <c r="H6" s="76" t="str">
+        <f t="shared" ref="H6:H8" si="3">IF(
+  AND(C6&gt;=$B$11, D6&gt;=$B$11),
+  "よく出来ました！",
+  IF(
+    AND(C6&gt;=$B$11, E6&gt;=$B$11),
+    "よく出来ました！",
+    IF(
+      AND(D6&gt;=$B$11, E6&gt;=$B$11),
+      "よく出来ました！",
+      ""
+    )
+  )
+)</f>
+        <v>よく出来ました！</v>
+      </c>
+      <c r="I6" s="76" t="str">
         <f t="shared" si="2"/>
-        <v>よく出来ました！</v>
-      </c>
-      <c r="I6" s="76" t="str">
-        <f t="shared" si="3"/>
         <v>よく出来ました！</v>
       </c>
     </row>
@@ -3325,11 +3361,11 @@
         <v/>
       </c>
       <c r="H7" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v>よく出来ました！</v>
+      </c>
+      <c r="I7" s="76" t="str">
         <f t="shared" si="2"/>
-        <v>よく出来ました！</v>
-      </c>
-      <c r="I7" s="76" t="str">
-        <f t="shared" si="3"/>
         <v>よく出来ました！</v>
       </c>
     </row>
@@ -3355,11 +3391,11 @@
         <v>不合格</v>
       </c>
       <c r="H8" s="76" t="str">
+        <f t="shared" si="3"/>
+        <v>よく出来ました！</v>
+      </c>
+      <c r="I8" s="76" t="str">
         <f t="shared" si="2"/>
-        <v>よく出来ました！</v>
-      </c>
-      <c r="I8" s="76" t="str">
-        <f t="shared" si="3"/>
         <v>よく出来ました！</v>
       </c>
     </row>
@@ -3408,46 +3444,46 @@
   <sheetData>
     <row r="1" spans="2:11" ht="8" customHeight="1"/>
     <row r="2" spans="2:11">
-      <c r="B2" s="101" t="s">
+      <c r="B2" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
     </row>
     <row r="3" spans="2:11" ht="32.5">
-      <c r="B3" s="103" t="s">
+      <c r="B3" s="118" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="104"/>
+      <c r="C3" s="119"/>
+      <c r="D3" s="119"/>
+      <c r="E3" s="119"/>
+      <c r="F3" s="119"/>
+      <c r="G3" s="119"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="119"/>
+      <c r="J3" s="119"/>
+      <c r="K3" s="119"/>
     </row>
     <row r="4" spans="2:11" ht="18" customHeight="1">
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="120" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="106"/>
-      <c r="K4" s="106"/>
+      <c r="C4" s="121"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="121"/>
+      <c r="F4" s="121"/>
+      <c r="G4" s="121"/>
+      <c r="H4" s="121"/>
+      <c r="I4" s="121"/>
+      <c r="J4" s="121"/>
+      <c r="K4" s="121"/>
     </row>
     <row r="5" spans="2:11" ht="23.5">
       <c r="B5" s="22"/>
@@ -3462,13 +3498,13 @@
       <c r="K5" s="23"/>
     </row>
     <row r="6" spans="2:11" ht="21">
-      <c r="B6" s="107" t="s">
+      <c r="B6" s="122" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="107"/>
-      <c r="D6" s="107"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="107"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
       <c r="G6" s="24" t="s">
         <v>38</v>
       </c>
@@ -3476,10 +3512,10 @@
       <c r="I6" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="108" t="s">
+      <c r="J6" s="123" t="s">
         <v>71</v>
       </c>
-      <c r="K6" s="96"/>
+      <c r="K6" s="111"/>
     </row>
     <row r="7" spans="2:11">
       <c r="B7" s="23"/>
@@ -3494,10 +3530,10 @@
       <c r="K7" s="26"/>
     </row>
     <row r="8" spans="2:11" ht="18" customHeight="1">
-      <c r="B8" s="109" t="s">
+      <c r="B8" s="124" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="109"/>
+      <c r="C8" s="124"/>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="27"/>
@@ -3514,10 +3550,10 @@
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="94"/>
+      <c r="C9" s="109"/>
       <c r="D9" s="27"/>
       <c r="E9" s="27"/>
       <c r="F9" s="27"/>
@@ -3573,10 +3609,10 @@
       <c r="K12" s="23"/>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="96"/>
+      <c r="C13" s="111"/>
       <c r="D13" s="39" t="s">
         <v>44</v>
       </c>
@@ -3599,24 +3635,24 @@
       <c r="K13" s="43"/>
     </row>
     <row r="14" spans="2:11">
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="112" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="98"/>
+      <c r="C14" s="113"/>
       <c r="D14" s="44"/>
       <c r="E14" s="45"/>
       <c r="F14" s="46"/>
       <c r="G14" s="47"/>
       <c r="H14" s="45"/>
-      <c r="I14" s="99"/>
-      <c r="J14" s="100"/>
-      <c r="K14" s="98"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="115"/>
+      <c r="K14" s="113"/>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="110" t="s">
+      <c r="B15" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="111"/>
+      <c r="C15" s="102"/>
       <c r="D15" s="48"/>
       <c r="E15" s="49">
         <v>300000</v>
@@ -3631,15 +3667,15 @@
         <f>E15*F15</f>
         <v>300000</v>
       </c>
-      <c r="I15" s="112"/>
-      <c r="J15" s="113"/>
-      <c r="K15" s="114"/>
+      <c r="I15" s="103"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="107"/>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="115" t="s">
+      <c r="B16" s="101" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="111"/>
+      <c r="C16" s="102"/>
       <c r="D16" s="48"/>
       <c r="E16" s="49">
         <v>45000</v>
@@ -3654,15 +3690,15 @@
         <f>E16*F16</f>
         <v>225000</v>
       </c>
-      <c r="I16" s="112"/>
-      <c r="J16" s="113"/>
-      <c r="K16" s="114"/>
+      <c r="I16" s="103"/>
+      <c r="J16" s="106"/>
+      <c r="K16" s="107"/>
     </row>
     <row r="17" spans="2:11">
-      <c r="B17" s="115" t="s">
+      <c r="B17" s="101" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="111"/>
+      <c r="C17" s="102"/>
       <c r="D17" s="44"/>
       <c r="E17" s="49">
         <v>1358</v>
@@ -3677,53 +3713,53 @@
         <f>E17*F17</f>
         <v>1358</v>
       </c>
-      <c r="I17" s="112" t="s">
+      <c r="I17" s="103" t="s">
         <v>60</v>
       </c>
-      <c r="J17" s="113"/>
-      <c r="K17" s="114"/>
+      <c r="J17" s="106"/>
+      <c r="K17" s="107"/>
     </row>
     <row r="18" spans="2:11">
-      <c r="B18" s="115" t="s">
+      <c r="B18" s="101" t="s">
         <v>62</v>
       </c>
-      <c r="C18" s="111"/>
+      <c r="C18" s="102"/>
       <c r="D18" s="44"/>
       <c r="E18" s="49"/>
       <c r="F18" s="53"/>
       <c r="G18" s="51"/>
       <c r="H18" s="52"/>
-      <c r="I18" s="112"/>
-      <c r="J18" s="113"/>
-      <c r="K18" s="114"/>
+      <c r="I18" s="103"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="107"/>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="115"/>
-      <c r="C19" s="111"/>
+      <c r="B19" s="101"/>
+      <c r="C19" s="102"/>
       <c r="D19" s="44"/>
       <c r="E19" s="49"/>
       <c r="F19" s="54"/>
       <c r="G19" s="51"/>
       <c r="H19" s="52"/>
-      <c r="I19" s="112"/>
-      <c r="J19" s="113"/>
-      <c r="K19" s="114"/>
+      <c r="I19" s="103"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="107"/>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" s="115"/>
-      <c r="C20" s="111"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="102"/>
       <c r="D20" s="44"/>
       <c r="E20" s="49"/>
       <c r="F20" s="55"/>
       <c r="G20" s="51"/>
       <c r="H20" s="52"/>
-      <c r="I20" s="112"/>
-      <c r="J20" s="113"/>
-      <c r="K20" s="114"/>
+      <c r="I20" s="103"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="107"/>
     </row>
     <row r="21" spans="2:11">
-      <c r="B21" s="115"/>
-      <c r="C21" s="111"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="102"/>
       <c r="D21" s="44"/>
       <c r="E21" s="49"/>
       <c r="F21" s="55"/>
@@ -3734,8 +3770,8 @@
       <c r="K21" s="58"/>
     </row>
     <row r="22" spans="2:11">
-      <c r="B22" s="115"/>
-      <c r="C22" s="111"/>
+      <c r="B22" s="101"/>
+      <c r="C22" s="102"/>
       <c r="D22" s="48"/>
       <c r="E22" s="49"/>
       <c r="F22" s="59"/>
@@ -3746,8 +3782,8 @@
       <c r="K22" s="58"/>
     </row>
     <row r="23" spans="2:11">
-      <c r="B23" s="115"/>
-      <c r="C23" s="111"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="102"/>
       <c r="D23" s="48"/>
       <c r="E23" s="49"/>
       <c r="F23" s="55"/>
@@ -3758,8 +3794,8 @@
       <c r="K23" s="58"/>
     </row>
     <row r="24" spans="2:11">
-      <c r="B24" s="115"/>
-      <c r="C24" s="111"/>
+      <c r="B24" s="101"/>
+      <c r="C24" s="102"/>
       <c r="D24" s="48"/>
       <c r="E24" s="49"/>
       <c r="F24" s="55"/>
@@ -3770,8 +3806,8 @@
       <c r="K24" s="58"/>
     </row>
     <row r="25" spans="2:11">
-      <c r="B25" s="115"/>
-      <c r="C25" s="111"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="102"/>
       <c r="D25" s="48"/>
       <c r="E25" s="49"/>
       <c r="F25" s="55"/>
@@ -3782,8 +3818,8 @@
       <c r="K25" s="58"/>
     </row>
     <row r="26" spans="2:11">
-      <c r="B26" s="115"/>
-      <c r="C26" s="111"/>
+      <c r="B26" s="101"/>
+      <c r="C26" s="102"/>
       <c r="D26" s="60"/>
       <c r="E26" s="61"/>
       <c r="F26" s="62"/>
@@ -3794,8 +3830,8 @@
       <c r="K26" s="58"/>
     </row>
     <row r="27" spans="2:11">
-      <c r="B27" s="115"/>
-      <c r="C27" s="111"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="102"/>
       <c r="D27" s="48"/>
       <c r="E27" s="49"/>
       <c r="F27" s="49"/>
@@ -3806,8 +3842,8 @@
       <c r="K27" s="58"/>
     </row>
     <row r="28" spans="2:11">
-      <c r="B28" s="115"/>
-      <c r="C28" s="111"/>
+      <c r="B28" s="101"/>
+      <c r="C28" s="102"/>
       <c r="D28" s="48"/>
       <c r="E28" s="49"/>
       <c r="F28" s="49"/>
@@ -3818,8 +3854,8 @@
       <c r="K28" s="58"/>
     </row>
     <row r="29" spans="2:11">
-      <c r="B29" s="115"/>
-      <c r="C29" s="111"/>
+      <c r="B29" s="101"/>
+      <c r="C29" s="102"/>
       <c r="D29" s="48"/>
       <c r="E29" s="49"/>
       <c r="F29" s="49"/>
@@ -3830,8 +3866,8 @@
       <c r="K29" s="58"/>
     </row>
     <row r="30" spans="2:11">
-      <c r="B30" s="115"/>
-      <c r="C30" s="111"/>
+      <c r="B30" s="101"/>
+      <c r="C30" s="102"/>
       <c r="D30" s="48"/>
       <c r="E30" s="49"/>
       <c r="F30" s="49"/>
@@ -3842,34 +3878,34 @@
       <c r="K30" s="58"/>
     </row>
     <row r="31" spans="2:11">
-      <c r="B31" s="115"/>
-      <c r="C31" s="111"/>
+      <c r="B31" s="101"/>
+      <c r="C31" s="102"/>
       <c r="D31" s="48"/>
       <c r="E31" s="49"/>
       <c r="F31" s="49"/>
       <c r="G31" s="51"/>
       <c r="H31" s="52"/>
-      <c r="I31" s="112"/>
-      <c r="J31" s="123"/>
-      <c r="K31" s="124"/>
+      <c r="I31" s="103"/>
+      <c r="J31" s="104"/>
+      <c r="K31" s="105"/>
     </row>
     <row r="32" spans="2:11" ht="14.5" thickBot="1">
-      <c r="B32" s="116"/>
-      <c r="C32" s="117"/>
+      <c r="B32" s="94"/>
+      <c r="C32" s="95"/>
       <c r="D32" s="64"/>
       <c r="E32" s="65"/>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
-      <c r="I32" s="118"/>
-      <c r="J32" s="119"/>
-      <c r="K32" s="120"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="97"/>
+      <c r="K32" s="98"/>
     </row>
     <row r="33" spans="2:23" ht="17" thickTop="1">
-      <c r="B33" s="121" t="s">
+      <c r="B33" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="122"/>
+      <c r="C33" s="100"/>
       <c r="D33" s="68"/>
       <c r="E33" s="69"/>
       <c r="F33" s="70"/>
@@ -3926,15 +3962,22 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B4:K4"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="I17:K17"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="I18:K18"/>
@@ -3947,22 +3990,15 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="B4:K4"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="I31:K31"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
